--- a/datasets/validacao.xlsx
+++ b/datasets/validacao.xlsx
@@ -496,16 +496,16 @@
         <v>-1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -703,7 +703,7 @@
         <v>-1</v>
       </c>
       <c r="G8" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
@@ -919,7 +919,7 @@
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -992,10 +992,10 @@
         <v>-1</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K16" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/validacao.xlsx
+++ b/datasets/validacao.xlsx
@@ -493,10 +493,10 @@
         <v>-1</v>
       </c>
       <c r="G2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -528,7 +528,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -563,19 +563,19 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -598,19 +598,19 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -633,19 +633,19 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -668,19 +668,19 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -738,19 +738,19 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -773,7 +773,7 @@
         <v>-1</v>
       </c>
       <c r="G10" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
@@ -808,7 +808,7 @@
         <v>-1</v>
       </c>
       <c r="G11" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
@@ -913,7 +913,7 @@
         <v>-1</v>
       </c>
       <c r="G14" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
@@ -948,7 +948,7 @@
         <v>-1</v>
       </c>
       <c r="G15" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
@@ -983,16 +983,16 @@
         <v>-1</v>
       </c>
       <c r="G16" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>

--- a/datasets/validacao.xlsx
+++ b/datasets/validacao.xlsx
@@ -487,25 +487,25 @@
         <v>0.4334</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>3.4965</v>
       </c>
       <c r="F2" t="n">
         <v>-1</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3">
@@ -522,25 +522,25 @@
         <v>0.639</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>4.0352</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4">
@@ -557,7 +557,7 @@
         <v>0.5925</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.1016</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -592,25 +592,25 @@
         <v>0.203</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>3.0117</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6">
@@ -627,25 +627,25 @@
         <v>0.6124000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1.7749</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7">
@@ -662,7 +662,7 @@
         <v>0.4378</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.6439</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -697,10 +697,10 @@
         <v>0.7423</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>3.3932</v>
       </c>
       <c r="F8" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -732,7 +732,7 @@
         <v>0.2469</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1.5866</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
@@ -767,10 +767,10 @@
         <v>1.0359</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>3.3591</v>
       </c>
       <c r="F10" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -802,25 +802,25 @@
         <v>0.9222</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>3.7174</v>
       </c>
       <c r="F11" t="n">
         <v>-1</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="12">
@@ -837,7 +837,7 @@
         <v>0.6124000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>-0.6585</v>
       </c>
       <c r="F12" t="n">
         <v>-1</v>
@@ -872,10 +872,10 @@
         <v>0.9766</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>5.3532</v>
       </c>
       <c r="F13" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
@@ -907,25 +907,25 @@
         <v>0.5374</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>3.2189</v>
       </c>
       <c r="F14" t="n">
         <v>-1</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15">
@@ -942,25 +942,25 @@
         <v>0.9222</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>3.7174</v>
       </c>
       <c r="F15" t="n">
         <v>-1</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="16">
@@ -980,7 +980,7 @@
         <v>0.5515</v>
       </c>
       <c r="F16" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>

--- a/datasets/validacao.xlsx
+++ b/datasets/validacao.xlsx
@@ -490,22 +490,22 @@
         <v>3.4965</v>
       </c>
       <c r="F2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -525,22 +525,22 @@
         <v>4.0352</v>
       </c>
       <c r="F3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -805,22 +805,22 @@
         <v>3.7174</v>
       </c>
       <c r="F11" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -910,22 +910,22 @@
         <v>3.2189</v>
       </c>
       <c r="F14" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -945,22 +945,22 @@
         <v>3.7174</v>
       </c>
       <c r="F15" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">

--- a/datasets/validacao.xlsx
+++ b/datasets/validacao.xlsx
@@ -490,22 +490,22 @@
         <v>3.4965</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3">
@@ -525,22 +525,22 @@
         <v>4.0352</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4">
@@ -805,22 +805,22 @@
         <v>3.7174</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="12">
@@ -910,22 +910,22 @@
         <v>3.2189</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15">
@@ -945,22 +945,22 @@
         <v>3.7174</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="16">
